--- a/public/templates/template_baseline_12_elemen.xlsx
+++ b/public/templates/template_baseline_12_elemen.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,42 +29,58 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF17365D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <i val="1"/>
+      <color rgb="FF7F6000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
+      <name val="Carlito"/>
+      <color rgb="FF1F1F1F"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <b val="1"/>
-      <color rgb="000F172A"/>
+      <color rgb="FF1F4E78"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="001E293B"/>
-      <sz val="10"/>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Carlito"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001E40AF"/>
-      <sz val="10"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -70,24 +89,51 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E40AF"/>
-        <bgColor rgb="001E40AF"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FF2F75B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -95,25 +141,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF70AD47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF70AD47"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
       </bottom>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -121,10 +225,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -133,23 +237,63 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -157,38 +301,90 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,632 +751,855 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="54.875" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FORMULIR AUDIT BASELINE FIX (12 ELEMEN) — KANWIL KEMENTERIAN HUKUM KEPRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>FINAL BASELINE V1.0 — MITRA KINERJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Instrumen Standardisasi Verifikasi &amp; Pembekuan Data Awal Naskah Kerja Sama</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>P01 — PILOT UTAMA — Dewan Kerajinan Nasional Daerah Provinsi Kepulauan Riau</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Kode Naskah</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Status Portofolio</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+          <t>IDENTITAS NASKAH DAN KONTROL PEMERIKSAAN</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Kode naskah</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>[KODE NASKAH]</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Status portofolio</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Pilot Utama</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Mitra Kerja Sama</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Nama Calon / Mitra Kerja Sama</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Nama Pemeriksa</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Tim Pokja Data</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Judul Kerja Sama</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Judul Lengkap Naskah Kerja Sama</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Tanggal Pemeriksaan</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Nama pemeriksa</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>[NAMA PEMERIKSA]</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Mitra</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>[NAMA MITRA KERJA SAMA]</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Unit/Tim pemeriksa</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Pokja Data / pemeriksa naskah</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Jenis dokumen</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>PKS</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Nomor naskah</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Sesuai naskah/P2MA</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Tanggal pemeriksaan</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Tanggal Mulai</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Tanggal Berakhir</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cut-off Baseline</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Judul kerja sama</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>[JUDUL KERJA SAMA]</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Cut-off baseline</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Status Pengisian</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Tanggal mulai</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>45976</v>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Tanggal berakhir</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>47801</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Status pengisian</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>DALAM PROSES</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>FINAL BASELINE — Data awal berasal dari matriks scoring, naskah/P2MA, dan hasil pemeriksaan sampai cut-off 28 Agustus 2026. Status mencerminkan kondisi pada cut-off; perkembangan setelahnya dicatat melalui scorecard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Kelompok</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Elemen Baseline</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Yang Diperiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Sumber/Bukti Minimum</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Elemen baseline</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Yang diperiksa</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Sumber/bukti minimum</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Fakta/Hasil Pemeriksaan</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Sumber/Link Bukti</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Catatan Khusus (Opsional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Fakta/hasil pemeriksaan</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Sumber/link bukti</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Catatan khusus (opsional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="69" customHeight="1">
+      <c r="A13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>IDENTITAS</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Identitas naskah</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Jenis, nomor para pihak, judul, keabsahan tanda tangan</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Naskah bertanda tangan; P2MA screenshot/link; register resmi</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Jenis, nomor para pihak, judul, dan nama resmi mitra sesuai naskah.</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Naskah bertanda tangan; P2MA sebagai pembanding.</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="11" t="n">
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14" ht="61.5" customHeight="1">
+      <c r="A14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>MASA BERLAKU</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Masa berlaku</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Tanggal efektif, durasi, dan tanggal berakhir naskah</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Klausul jangka waktu; halaman tanda tangan; konfirmasi unit</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Tanggal efektif, durasi, dan tanggal berakhir sesuai klausul naskah.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Klausul jangka waktu; halaman tanda tangan; P2MA.</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="G14" s="17" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="17" t="inlineStr"/>
+    </row>
+    <row r="15" ht="81" customHeight="1">
+      <c r="A15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>SUBSTANSI</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Ruang lingkup</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Ruang kerja, kewajiban, atau komitmen para pihak</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Pasal ruang lingkup/hak-kewajiban; lampiran teknis bila ada</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Ruang kerja, kewajiban, atau kegiatan utama yang disepakati.</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Pasal ruang lingkup/hak-kewajiban; lampiran.</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="11" t="n">
+      <c r="G15" s="17" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="17" t="inlineStr"/>
+    </row>
+    <row r="16" ht="61.5" customHeight="1">
+      <c r="A16" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>TATA KELOLA</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Status arsip</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Ketersediaan naskah lengkap pada unit kerja/pengelola</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Arsip resmi; register; folder elektronik unit pengampu</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Ketersediaan naskah lengkap pada lokasi arsip resmi dan dapat ditemukan kembali.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Arsip resmi; register; folder organisasi.</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="G16" s="17" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>TATA KELOLA</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Status P2MA</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Keberadaan entri dan kesesuaian data pada aplikasi P2MA</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>P2MA dan naskah bertanda tangan; nomor/tanggal sinkron</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Keberadaan entri dan kesesuaian metadata P2MA dengan naskah resmi.</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>P2MA dan naskah bertanda tangan.</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="11" t="n">
+      <c r="G17" s="17" t="inlineStr"/>
+      <c r="H17" s="17" t="inlineStr"/>
+      <c r="I17" s="17" t="inlineStr"/>
+    </row>
+    <row r="18" ht="61.5" customHeight="1">
+      <c r="A18" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>PENGAMPU</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Unit pengampu</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Unit internal yang bertanggung jawab atas pelaksanaan</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>ND/SK/pembagian tugas; konfirmasi tertulis unit pemangku</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Unit internal yang bertanggung jawab atas substansi dan implementasi kerja sama.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>ND/SK/pembagian tugas; konfirmasi tertulis unit.</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="12" t="inlineStr"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="8" t="n">
+      <c r="G18" s="17" t="inlineStr"/>
+      <c r="H18" s="17" t="inlineStr"/>
+      <c r="I18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19" ht="61.5" customHeight="1">
+      <c r="A19" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>PIC</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>PIC internal</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>PIC utama dan cadangan yang aktif dari pihak internal</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>ND/SK/daftar PIC; konfirmasi tertulis unit pemangku</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>PIC utama dan cadangan yang aktif, lengkap dengan jabatan, kontak, dan dasar penetapan.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>ND/SK/daftar PIC; konfirmasi tertulis unit.</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="11" t="n">
+      <c r="G19" s="17" t="inlineStr"/>
+      <c r="H19" s="17" t="inlineStr"/>
+      <c r="I19" s="17" t="inlineStr"/>
+    </row>
+    <row r="20" ht="61.5" customHeight="1">
+      <c r="A20" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>PIC</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>PIC mitra</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Penghubung operasional pihak mitra yang dapat dihubungi</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>Surat/email/form konfirmasi resmi dari mitra kerja sama</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Penghubung operasional pihak mitra yang telah dikonfirmasi.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Surat/email/form konfirmasi resmi dari mitra.</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="8" t="n">
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="61.5" customHeight="1">
+      <c r="A21" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>TINDAK LANJUT</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Rencana tindak lanjut</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Dokumen atau komitmen operasional setelah penandatanganan</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Rencana aksi; matriks kerja; kalender tindak lanjut bersama</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Dokumen atau komitmen operasional yang memuat kegiatan, periode, target, dan/atau PIC.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Rencana aksi; matriks kerja; kalender; notula.</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="11" t="n">
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="17" t="inlineStr"/>
+    </row>
+    <row r="22" ht="61.5" customHeight="1">
+      <c r="A22" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>PELAKSANAAN</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>Pelaksanaan dan hasil</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Kegiatan aktual, realisasi tertentu, atau status belum jalan</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Laporan; undangan; notula; daftar hadir; dokumentasi fisik</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Kegiatan aktual, realisasi terhadap target jatuh tempo, serta output yang dihasilkan.</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>Laporan; undangan; notula; daftar hadir; data hasil.</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="12" t="inlineStr"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="8" t="n">
+      <c r="G22" s="22" t="inlineStr"/>
+      <c r="H22" s="22" t="inlineStr"/>
+      <c r="I22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23" ht="61.5" customHeight="1">
+      <c r="A23" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>EVIDEN</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Eviden implementasi</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Bukti pelaksanaan/output, lokasi penyimpanan berkas</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Folder resmi; indeks bukti; dokumen/data dukung kegiatan</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Bukti pelaksanaan/output, lokasi penyimpanan, dan tingkat keteraturannya.</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Folder resmi; indeks bukti; dokumen/data kegiatan.</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-      <c r="I22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="11" t="n">
+      <c r="G23" s="17" t="inlineStr"/>
+      <c r="H23" s="17" t="inlineStr"/>
+      <c r="I23" s="17" t="inlineStr"/>
+    </row>
+    <row r="24" ht="75" customHeight="1">
+      <c r="A24" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>HAMBATAN</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Hambatan/gap</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Kendala faktual atau kekosongan yang perlu ditangani</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>Konfirmasi unit/PIC/mitra; notula monev; catatan audit</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Kendala faktual atau kekosongan data yang memengaruhi implementasi dan sudah dikonfirmasi.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Konfirmasi unit/PIC/mitra; notula; laporan; bukti keterlambatan.</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>BELUM DIISI</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
+      <c r="G24" s="17" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr"/>
+      <c r="I24" s="17" t="inlineStr"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>RINGKASAN FINAL BASELINE</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>STATUS ELEMEN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>JUMLAH</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>INDIKATOR PENGISIAN</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>HASIL</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>RINGKASAN PEMERIKSA</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="28.5" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Terverifikasi</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>COUNTIF(F13:F24,"TERVERIFIKASI")</f>
+        <v/>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Kelengkapan pemeriksaan</t>
+        </is>
+      </c>
+      <c r="E29" s="25">
+        <f>COUNTIFS(F13:F24,"&lt;&gt;",G13:G24,"&lt;&gt;",H13:H24,"&lt;&gt;")/12</f>
+        <v/>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Fakta utama</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>Identitas naskah, masa berlaku, ruang lingkup, dan entri P2MA telah terverifikasi. Arsip khusus belum tersedia dan pada cut-off belum ada laporan pelaksanaan yang dapat dijadikan bukti hasil.</t>
+        </is>
+      </c>
+      <c r="I29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="28.5" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Belum Terverifikasi</t>
+        </is>
+      </c>
+      <c r="B30" s="24">
+        <f>COUNTIF(F13:F24,"BELUM TERVERIFIKASI")</f>
+        <v/>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Proporsi status terverifikasi</t>
+        </is>
+      </c>
+      <c r="E30" s="25">
+        <f>IFERROR(B29/(12-B32),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="29" t="n"/>
+      <c r="I30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="28.5" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Belum Tersedia</t>
+        </is>
+      </c>
+      <c r="B31" s="24">
+        <f>COUNTIF(F13:F24,"BELUM TERSEDIA")</f>
+        <v/>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Status pengisian baseline</t>
+        </is>
+      </c>
+      <c r="E31" s="31">
+        <f>IF(E29=0,"BELUM DIMULAI",IF(E29=1,"SELESAI DIISI","DALAM VERIFIKASI"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>Gap utama</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
+        <is>
+          <t>Unit pengampu, PIC internal/mitra, rencana tindak lanjut, eviden implementasi, dan hambatan belum memiliki dasar yang cukup. Kerja sama belum menunjukkan bukti operasional yang terstruktur pada cut-off.</t>
+        </is>
+      </c>
+      <c r="I31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="28.5" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Tidak Relevan</t>
+        </is>
+      </c>
+      <c r="B32" s="24">
+        <f>COUNTIF(F13:F24,"TIDAK RELEVAN")</f>
+        <v/>
+      </c>
+      <c r="G32" s="26" t="n"/>
+      <c r="H32" s="29" t="n"/>
+      <c r="I32" s="30" t="n"/>
+    </row>
+    <row r="33" ht="28.5" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Belum Diisi</t>
+        </is>
+      </c>
+      <c r="B33" s="24">
+        <f>COUNTBLANK(F13:F24)</f>
+        <v/>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>Catatan transisi</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="inlineStr">
+        <is>
+          <t>Kondisi ini dikunci sebagai baseline. Penetapan pengampu/PIC, rencana aksi, pelaksanaan, dan eviden berikutnya dimutakhirkan melalui scorecard.</t>
+        </is>
+      </c>
+      <c r="I33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="28.5" customHeight="1">
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="30" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="28.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Final baseline per 28 Agustus 2026. Baseline merupakan potret kondisi awal; pemutakhiran bukti, konfirmasi, dan progres setelah cut-off dilakukan melalui scorecard.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B5:D5"/>
+  <mergeCells count="23">
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="H31:I32"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H8:I8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F12:F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TERVERIFIKASI,BELUM TERVERIFIKASI,BELUM TERSEDIA,TIDAK RELEVAN,BELUM DIISI"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>